--- a/data/trans_bre/IP19C06-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C06-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 11,41</t>
+          <t>-5,78; 14,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 0,0</t>
+          <t>-6,21; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 0,0</t>
+          <t>-7,54; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 11,18</t>
+          <t>-6,88; 10,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,37</t>
+          <t>0,0; 5,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 13,58</t>
+          <t>1,56; 13,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,43</t>
+          <t>0,0; 24,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 0,0</t>
+          <t>-15,05; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 6,52</t>
+          <t>-0,95; 5,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 4,35</t>
+          <t>-1,71; 4,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 0,0</t>
+          <t>-5,54; 0,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,24</t>
+          <t>0,0; 3,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,45</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1460,22 +1460,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,0</t>
+          <t>-1,2; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,42</t>
+          <t>-0,67; 1,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,1</t>
+          <t>-0,38; 0,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,16</t>
+          <t>-0,1; 2,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-78,95; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-52,24; —</t>
+          <t>-51,27; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C06-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C06-Provincia-trans_bre.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 14,31</t>
+          <t>-5,84; 11,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 0,0</t>
+          <t>-6,08; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 0,0</t>
+          <t>-7,52; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 10,58</t>
+          <t>-7,66; 10,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,89</t>
+          <t>0,0; 5,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 13,88</t>
+          <t>1,68; 14,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,96</t>
+          <t>0,0; 22,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 0,0</t>
+          <t>-9,27; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 5,87</t>
+          <t>-1,64; 5,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 4,38</t>
+          <t>-1,73; 4,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 0,0</t>
+          <t>-5,33; 0,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,0; 3,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 4,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1460,22 +1460,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,0</t>
+          <t>-1,25; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,51</t>
+          <t>-0,75; 1,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,97</t>
+          <t>-0,38; 0,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 2,18</t>
+          <t>-0,14; 2,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,1; 749,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-51,27; —</t>
+          <t>-67,49; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C06-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C06-Provincia-trans_bre.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 11,44</t>
+          <t>-5,84; 11,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 0,0</t>
+          <t>-6,17; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,58</t>
+          <t>3,89</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>215,3%</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 0,0</t>
+          <t>-6,89; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 10,25</t>
+          <t>-2,03; 13,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,42</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,23</t>
+          <t>0,0; 5,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 14,63</t>
+          <t>1,64; 13,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,33</t>
+          <t>0,0; 21,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 0,0</t>
+          <t>-11,03; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>108,33%</t>
+          <t>111,28%</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 5,49</t>
+          <t>-1,48; 6,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 4,11</t>
+          <t>-1,48; 4,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 0,0</t>
+          <t>-4,67; 0,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,29</t>
+          <t>0,0; 4,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,47</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>199,63%</t>
+          <t>312,44%</t>
         </is>
       </c>
     </row>
@@ -1460,22 +1460,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,0</t>
+          <t>-1,12; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,44</t>
+          <t>-0,69; 1,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,94</t>
+          <t>-0,38; 1,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,24</t>
+          <t>0,18; 2,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-84,1; 749,61</t>
+          <t>-78,95; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-67,49; —</t>
+          <t>-35,58; —</t>
         </is>
       </c>
     </row>
